--- a/04_人工交叉验证与最终纳入/论文最终分类汇总.xlsx
+++ b/04_人工交叉验证与最终纳入/论文最终分类汇总.xlsx
@@ -2145,7 +2145,7 @@
         <x:v>Automated and effective metamorphic testing: relation discovery, deduction, and generation</x:v>
       </x:c>
       <x:c r="E38" s="15" t="n">
-        <x:v>2025</x:v>
+        <x:v>2026</x:v>
       </x:c>
       <x:c r="F38" s="3" t="str">
         <x:v>原有</x:v>
